--- a/src/test/resources/DemoWebShop_TestDataa.xlsx
+++ b/src/test/resources/DemoWebShop_TestDataa.xlsx
@@ -3,14 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nanditha HK\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9127CE40-5B03-4209-A267-8E3D27543EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{12272324-6FBC-432D-93BA-D2F16A394A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SignupLoginData" sheetId="1" r:id="rId1"/>
@@ -21,6 +16,7 @@
     <sheet name="LogoutData" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:H8"/>
 </workbook>
 </file>
 
